--- a/Capitulo_05/Cap05_Politica_Copias_Seguridad.xlsx
+++ b/Capitulo_05/Cap05_Politica_Copias_Seguridad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://openitsoft-my.sharepoint.com/personal/mvergara_openitnet_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://openitsoft-my.sharepoint.com/personal/mvergara_openitnet_com/Documents/Libro MPC/Capitulos/05- Datos/Templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_1C61069AFFCE80FB8B4212D54690268F4E55AE09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF0BB9E0-E76E-481F-9441-A9A593EFCE8C}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_1C61069AFFCE80FB8B4212D54690268F4E55AE09" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D50C0F5-D8A3-4CB3-ABD8-68C6A04E2D87}"/>
   <bookViews>
-    <workbookView xWindow="30825" yWindow="1170" windowWidth="22620" windowHeight="13050" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="1125" windowWidth="21600" windowHeight="11505" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Generales" sheetId="1" r:id="rId1"/>
@@ -840,124 +840,124 @@
   </cellStyleXfs>
   <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1295,369 +1295,389 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
     </row>
     <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
     </row>
     <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
     </row>
     <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
     </row>
     <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
     </row>
     <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" spans="1:6" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
     </row>
     <row r="18" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
     </row>
     <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
     </row>
     <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
     </row>
     <row r="26" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
     </row>
     <row r="27" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
     </row>
     <row r="28" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
     </row>
     <row r="29" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
     </row>
     <row r="30" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="C25:F25"/>
@@ -1665,26 +1685,6 @@
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1709,692 +1709,692 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
     </row>
     <row r="2" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
     </row>
     <row r="4" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="14" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="16">
         <v>7</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="J5" s="30" t="s">
+      <c r="J5" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="K5" s="30" t="s">
+      <c r="K5" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="L5" s="15" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="18">
         <v>5</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="J6" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="K6" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="L6" s="31" t="s">
+      <c r="L6" s="17" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="16">
         <v>4</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="K7" s="30" t="s">
+      <c r="K7" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="18">
         <v>3</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="32" t="s">
+      <c r="K8" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="L8" s="31" t="s">
+      <c r="L8" s="17" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="16">
         <v>4</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="J9" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="K9" s="30" t="s">
+      <c r="K9" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L9" s="29" t="s">
+      <c r="L9" s="15" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="18">
         <v>5</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H10" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="J10" s="32" t="s">
+      <c r="J10" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="32" t="s">
+      <c r="K10" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="L10" s="31"/>
+      <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="22"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="22"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="22"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="22"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
     </row>
     <row r="35" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="33">
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="19">
         <f>COUNTA(C5:C34)</f>
         <v>6</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="33">
+      <c r="H35" s="39"/>
+      <c r="I35" s="19">
         <f>COUNTIF(B5:B34,"Crítica")</f>
         <v>4</v>
       </c>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
+      <c r="J35" s="40"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="40"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2457,26 +2457,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
     </row>
     <row r="2" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
     </row>
     <row r="3" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
@@ -2490,268 +2490,268 @@
       <c r="G3" s="41"/>
     </row>
     <row r="4" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="14" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F5" s="34" t="s">
+      <c r="F5" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="2" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="F9" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="34" t="s">
+      <c r="F13" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="35" t="s">
+      <c r="F14" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
     </row>
     <row r="16" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="42" t="s">
@@ -2774,15 +2774,15 @@
       <c r="G17" s="42"/>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2809,108 +2809,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="2" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="38" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="37" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
     </row>
     <row r="4" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="14" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="1" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="2" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="42" t="s">
@@ -2929,13 +2929,13 @@
       <c r="E10" s="42"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2962,161 +2962,161 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
     </row>
     <row r="2" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="14" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="2" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="2" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="2" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="2" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="1" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="2" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
